--- a/vocabulary_list.xlsx
+++ b/vocabulary_list.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3356,6 +3356,8316 @@
         </is>
       </c>
     </row>
+    <row r="52" ht="50" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>agenda</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>議題</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Let's move on to the next item on the agenda.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>議題の次の項目に移りましょう。</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="50" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>議事録</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>I'll send the meeting minutes by tomorrow.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>明日までに議事録を送ります。</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>会議の「議事録」の意味では常に複数形で使う。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="50" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>attend</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>出席する</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Will you be able to attend the meeting on Friday?</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>金曜日の会議に出席できますか。</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>契約</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>We signed the contract last week.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>先週、契約を締結しました。</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="50" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>approve</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>承認する</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>The manager approved the budget proposal.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>マネージャーが予算案を承認しました。</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>却下する</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>The client rejected our first proposal.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>クライアントは最初の提案を却下しました。</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>revise</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>修正する</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Can you revise the report by tomorrow?</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>明日までに報告書を修正してもらえますか。</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="50" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>submit</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>提出する</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Please submit your expense report by Friday.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>金曜日までに経費報告書を提出してください。</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="50" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>confirm</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>確認する</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>I just want to confirm our meeting time.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>打ち合わせの時間を確認したいだけです。</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="50" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>postpone</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>延期する</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>We had to postpone the launch by a week.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>発売を1週間延期する必要がありました。</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="50" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>cancel</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>キャンセルする</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>The client canceled the order at the last minute.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>クライアントは直前に注文をキャンセルしました。</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>attach</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>添付する</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>I've attached the file to this email.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>このメールにファイルを添付しました。</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="50" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>転送する</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Could you forward this email to the sales team?</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>このメールを営業チームに転送してもらえますか。</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>reply</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>返信する</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>I'll reply to your message as soon as possible.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>できるだけ早くメッセージに返信します。</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>respond</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="50" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>remind</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>念を押す・思い出させる</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Please remind me to call the client tomorrow.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>明日クライアントに電話するよう私に念押ししてください。</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="50" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>上司・監督者</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>My supervisor reviews all outgoing emails.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>私の上司はすべての送信メールを確認します。</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="50" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>She transferred to the marketing department.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>彼女はマーケティング部に異動しました。</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="50" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>headquarters</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>The headquarters is located in Tokyo.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>本社は東京にあります。</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>単数扱いで使われることが多い。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="50" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>支社・支店</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>We opened a new branch in Osaka.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>大阪に新しい支店を開設しました。</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="50" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>業者・仕入れ先</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>We switched to a new vendor for office supplies.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>事務用品の仕入れ先を新しい業者に変更しました。</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>supplier</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="50" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>shipment</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>出荷・発送</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>The shipment is expected to arrive next Monday.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>出荷分は来週月曜日に到着予定です。</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="50" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>在庫</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>We need to check the inventory before ordering more.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>追加発注する前に在庫を確認する必要があります。</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="50" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>倉庫</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>The products are stored in a warehouse near the port.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>製品は港近くの倉庫に保管されています。</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="50" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>割引</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>We offer a 10% discount for bulk orders.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>大量注文には10%の割引を提供しています。</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="50" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>refund</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>返金</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>The customer asked for a full refund.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>顧客は全額返金を求めました。</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="50" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>receipt</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>領収書</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Please keep the receipt for your records.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>記録のため領収書を保管しておいてください。</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="50" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>見積もり</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Can you send us a quote for the project?</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>そのプロジェクトの見積もりを送っていただけますか。</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="50" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>サンプル・見本</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>We'd like to request a free sample.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>無料サンプルをリクエストしたいのですが。</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="50" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>アンケート・調査</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>We sent a customer satisfaction survey last week.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>先週、顧客満足度アンケートを送付しました。</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="50" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>announcement</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>お知らせ・発表</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>The CEO made an announcement about the merger.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>CEOが合併について発表しました。</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="50" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>handout</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>配布資料</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Please take a handout from the table.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>テーブルから配布資料を1部お取りください。</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="50" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>overtime</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>残業</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>I had to work overtime to finish the report.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>報告書を仕上げるために残業しなければなりませんでした。</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="50" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>シフト・勤務時間帯</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>She works the night shift twice a week.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>彼女は週に2回夜勤シフトで働いています。</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="50" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>absence</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>欠勤</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Please notify HR in case of absence.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>欠勤する場合は人事に連絡してください。</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="50" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>vacation</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>休暇</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>I'm planning to take a vacation next month.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>来月休暇を取る予定です。</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="50" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>resign</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>退職する</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>He decided to resign from his position.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>彼は退職することを決めました。</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="50" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>hire</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>雇う</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>We're planning to hire two new engineers.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>エンジニアを2名新たに雇う予定です。</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="50" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>昇進させる</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>She was promoted to team leader last month.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>彼女は先月チームリーダーに昇進しました。</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="50" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>reschedule</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>予定を変更する</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Can we reschedule the meeting to next week?</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>会議を来週に予定変更できますか。</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="50" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>clarify</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>明確にする</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Could you clarify what you mean by that?</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>それがどういう意味か明確にしてもらえますか。</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="50" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>調達</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>The procurement team is negotiating with three suppliers.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>調達チームは3社のサプライヤーと交渉しています。</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="50" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Logistics has become more complex since we expanded overseas.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>海外展開してから物流はより複雑になりました。</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="50" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>forecast</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>予測</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Our sales forecast for next quarter looks promising.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>来四半期の売上予測は好調に見えます。</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>動詞としても使い、その場合「予測する」という意味になる。</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="50" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>四半期</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Revenue grew 8% in the third quarter.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>第3四半期の収益は8%成長しました。</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="50" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>fiscal year</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>会計年度</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Our fiscal year starts in April.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>当社の会計年度は4月に始まります。</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="50" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>net profit</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>純利益</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Net profit increased despite rising costs.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>コスト上昇にもかかわらず純利益は増加しました。</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="50" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>gross revenue</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>総収益</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Gross revenue reached a record high this year.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>今年、総収益は過去最高を記録しました。</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="50" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>break-even</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>損益分岐点</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>We expect to reach break-even within two years.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2年以内に損益分岐点に達すると見込んでいます。</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="50" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>cash flow</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>キャッシュフロー</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>We need to improve our cash flow before expanding.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>拡大する前にキャッシュフローを改善する必要があります。</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="50" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>資産</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Our biggest asset is our experienced team.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>私たちの最大の資産は経験豊富なチームです。</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="50" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>liability</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>負債</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>The company reduced its liabilities significantly last year.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>その会社は昨年、負債を大幅に削減しました。</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="50" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>株式・自己資本</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>The founders retained 60% equity in the company.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>創業者たちは会社の株式の60%を保持しました。</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="50" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>dividend</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>配当</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>The company paid a higher dividend this quarter.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>その会社は今四半期、より高い配当を支払いました。</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="50" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>subsidiary</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>子会社</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>The subsidiary operates independently from the parent company.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>その子会社は親会社から独立して運営されています。</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="50" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>merger</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>合併</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>The merger is expected to close by year-end.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>その合併は年末までに完了する見込みです。</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="50" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>acquisition</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>買収</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>The acquisition doubled our customer base overnight.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>その買収により顧客基盤が一晩で倍増しました。</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="50" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>incentive</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>インセンティブ・奨励金</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Employees receive an incentive for meeting their targets.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>従業員は目標達成でインセンティブを受け取ります。</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="50" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>compensation</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>報酬・給与</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>The compensation package includes health insurance.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>報酬パッケージには健康保険が含まれています。</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="50" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>人員削減・解雇</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>The company announced layoffs in two departments.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>その会社は2つの部署で人員削減を発表しました。</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="50" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0110</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>turnaround</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>好転・立て直し</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>The new CEO led a remarkable turnaround.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>新しいCEOは目覚ましい業績回復を導きました。</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="50" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0111</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>downturn</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>景気後退</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Sales dropped sharply during the economic downturn.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>景気後退の間、売上は急落しました。</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="50" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0112</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>recession</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>不景気</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Many companies cut costs during the recession.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>多くの企業は不景気の間コストを削減しました。</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="50" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0113</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>inflation</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>インフレ</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Inflation has pushed up our material costs.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>インフレにより原材料費が上昇しました。</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="50" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0114</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>procure</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>調達する</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>We need to procure raw materials from a local supplier.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>地元の業者から原材料を調達する必要があります。</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="50" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0115</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>negotiate</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>交渉する</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>We're still negotiating the terms of the contract.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>契約条件についてまだ交渉中です。</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="50" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0116</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>finalize</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>確定させる</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Let's finalize the details before the meeting ends.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>会議が終わる前に詳細を確定させましょう。</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="50" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0117</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>implement</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>実行する・導入する</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>We plan to implement the new system next month.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>来月、新しいシステムを導入する予定です。</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="50" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0118</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>facilitate</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>促進する・円滑にする</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>The new tool facilitates communication between teams.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>その新しいツールはチーム間のコミュニケーションを円滑にします。</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="50" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0119</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>coordinate</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>調整する</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Please coordinate with the design team on this.</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>この件についてデザインチームと調整してください。</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="50" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0120</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>delegate</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>委任する</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>A good manager knows when to delegate tasks.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>優れたマネージャーはいつ業務を委任すべきか知っています。</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="50" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0121</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>supervise</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>監督する</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>She supervises a team of ten people.</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>彼女は10人のチームを監督しています。</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="50" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0122</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>underperform</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>期待を下回る</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>The product underperformed compared to expectations.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>その製品は期待を下回る結果となりました。</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="50" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0123</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>outperform</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>上回る・しのぐ</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Our new product outperformed the competition.</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>私たちの新製品は競合をしのぎました。</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="50" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0124</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>viable</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>実行可能な</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Is this plan financially viable?</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>この計画は財務的に実行可能ですか。</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="50" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0125</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>sustainable</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>持続可能な</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>We're looking for a more sustainable business model.</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>より持続可能なビジネスモデルを模索しています。</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="50" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0126</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>堅牢な・しっかりした</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>We need a more robust backup system.</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>より堅牢なバックアップシステムが必要です。</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="50" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0127</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>versatile</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>汎用性の高い・多才な</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>She's a versatile employee who can handle multiple roles.</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>彼女は複数の役割をこなせる多才な従業員です。</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="50" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0128</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>comprehensive</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>包括的な</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>The report offers a comprehensive overview of the market.</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>その報告書は市場の包括的な概観を提供しています。</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="50" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0129</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>透明性のある</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>We try to be transparent about our pricing.</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>私たちは価格について透明性を保つよう努めています。</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="50" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0130</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>仮の・暫定的な</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>We have a tentative agreement, pending final approval.</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>最終承認待ちですが、暫定的な合意には至っています。</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="50" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0131</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>preliminary</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>予備の・事前の</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>These are just preliminary results.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>これらはあくまで予備的な結果です。</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="50" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0132</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>subsequent</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>その後の</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Subsequent meetings will focus on implementation.</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>その後の会議は実行に焦点を当てます。</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="50" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0133</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>concurrent</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>同時進行の</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>We're running two concurrent projects this quarter.</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>今四半期は2つのプロジェクトを同時進行しています。</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="50" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0134</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>mandatory</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>義務的な・必須の</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Attendance at the training session is mandatory.</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>研修への出席は必須です。</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="50" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0135</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>契約上の</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>We have a contractual obligation to deliver by June.</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>6月までに納品する契約上の義務があります。</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="50" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0136</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>proficient</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>熟練した</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>She's proficient in both English and Spanish.</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>彼女は英語とスペイン語の両方に熟練しています。</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="50" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0137</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>keep someone posted</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>進捗を逐一報告する</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>I'll keep you posted on any updates.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>進展があれば逐一お知らせします。</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="50" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0138</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>on the same page</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>認識が一致している</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Let's make sure we're all on the same page before we start.</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>始める前に全員の認識が一致していることを確認しましょう。</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="50" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0139</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>get the ball rolling</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>物事を始動させる</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Let's get the ball rolling on this project.</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>このプロジェクトを始動させましょう。</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="50" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0140</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>in the pipeline</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>進行中で・準備中で</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>We have several new products in the pipeline.</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>いくつかの新製品が準備中です。</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="50" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0141</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>across the board</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>全体的に・一律に</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>We're cutting costs across the board.</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>全部門で一律にコストを削減しています。</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="50" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0142</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>up to speed</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>最新の状況を把握して</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Let me get you up to speed on the project.</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>プロジェクトの最新状況をお伝えします。</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="50" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0143</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>game plan</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>戦略・作戦</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>What's our game plan for the presentation?</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>プレゼンの作戦はどうしましょうか。</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="50" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0144</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>red tape</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>官僚的な手続き</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>It took months to cut through the red tape.</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>煩雑な手続きを乗り越えるのに数か月かかりました。</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="50" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0145</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>rule of thumb</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>経験則</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>As a rule of thumb, we allow two weeks for review.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>経験則として、確認には2週間見ています。</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="50" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0146</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>win-win</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>双方にとって有利な</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>This partnership is a win-win for both companies.</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>この提携は両社にとってウィンウィンです。</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="50" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0147</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>touchpoint</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>接点・タッチポイント</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Every customer touchpoint matters to our brand.</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>あらゆる顧客接点が私たちのブランドにとって重要です。</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="50" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0148</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>workaround</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>回避策</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>We found a workaround until the system is fixed.</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>システムが修正されるまでの回避策を見つけました。</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="50" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0149</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>bottleneck</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>ボトルネック・障害</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Approval delays are a major bottleneck in our process.</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>承認の遅れが私たちのプロセスの大きなボトルネックです。</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="50" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0150</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>roadmap</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>ロードマップ・行程表</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>We shared our product roadmap with the team.</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>製品のロードマップをチームと共有しました。</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="50" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0151</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>blueprint</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>設計図・青写真</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>This plan serves as a blueprint for future growth.</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>この計画は将来の成長の青写真となります。</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="50" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0152</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>framework</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>枠組み・フレームワーク</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>We developed a framework for evaluating new vendors.</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>新しい業者を評価するための枠組みを開発しました。</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="50" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0153</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>We track several key metrics every week.</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>毎週いくつかの主要な指標を追跡しています。</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="50" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0154</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>基準線・ベースライン</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>We need to establish a baseline before making changes.</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>変更を加える前に基準となる数値を設定する必要があります。</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="50" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0155</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>しきい値・基準</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Orders above this threshold qualify for free shipping.</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>この基準を超える注文は送料無料の対象になります。</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="50" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0156</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>variance</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>差異・ばらつき</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>There's a significant variance between the two reports.</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>2つの報告書の間に大きな差異があります。</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="50" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0157</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>discrepancy</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>食い違い・不一致</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>We found a discrepancy in the accounting figures.</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>会計数値に食い違いが見つかりました。</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="50" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0158</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>異常・例外</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>This month's drop in sales appears to be an anomaly.</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>今月の売上減少は例外的なもののようです。</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="50" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0159</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>overhaul</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>大幅な見直し・改革</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>The company underwent a complete overhaul of its IT systems.</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>その会社はITシステムの全面的な見直しを行いました。</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>動詞としても使い、その場合「大幅に見直す」という意味になる。</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="50" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0160</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>restructure</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>再編する</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>The company decided to restructure its sales division.</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>その会社は営業部門を再編することにしました。</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="50" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0161</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>arbitration</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>仲裁</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>The dispute was resolved through arbitration.</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>その紛争は仲裁により解決されました。</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="50" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0162</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>litigation</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>The company wants to avoid costly litigation.</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>その会社は費用のかかる訴訟を避けたいと考えています。</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="50" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0163</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>indemnify</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>補償する</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>The vendor agreed to indemnify us against any losses.</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>業者はいかなる損失に対しても当社を補償することに同意しました。</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="50" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0164</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>管轄権</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>This contract falls under the jurisdiction of Japanese law.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>この契約は日本法の管轄下にあります。</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="50" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0165</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>独占禁止の</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>The merger is under review by antitrust regulators.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>その合併は独占禁止法当局による審査を受けています。</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="50" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0166</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>fiduciary</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>受託者責任のある</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Board members have a fiduciary duty to shareholders.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>取締役会メンバーは株主に対して受託者責任を負っています。</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="50" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0167</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>covenant</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>誓約・契約条項</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>The loan agreement includes several financial covenants.</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>その融資契約にはいくつかの財務上の誓約条項が含まれています。</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="50" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0168</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>tacit</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>暗黙の</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>There was a tacit understanding between the two parties.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>両者の間には暗黙の了解がありました。</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="50" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0169</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>ambiguous</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>曖昧な</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>The wording of the clause is dangerously ambiguous.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>その条項の文言は危険なほど曖昧です。</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="50" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0170</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>equitable</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>公平な</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>We aim to reach an equitable solution for both sides.</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>双方にとって公平な解決策を目指しています。</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="50" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0171</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>exacerbate</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>悪化させる</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Delays in shipping exacerbated the customer complaints.</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>配送の遅れが顧客からの苦情を悪化させました。</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="50" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0172</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>contingent</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>条件付きの・〜次第の</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>The offer is contingent on final board approval.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>そのオファーは取締役会の最終承認次第です。</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="50" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0173</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>expedite</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>迅速に進める</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Can you expedite the shipping process for this order?</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>この注文の発送プロセスを迅速に進めてもらえますか。</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="50" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0174</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>circumvent</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>回避する・迂回する</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>They found a way to circumvent the approval process.</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>彼らは承認プロセスを回避する方法を見つけました。</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="50" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0175</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>capitalize on</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>〜を活用する</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>We should capitalize on this market opportunity while we can.</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>できるうちにこの市場機会を活用すべきです。</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="50" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0176</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>spearhead</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>先頭に立って進める</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>She will spearhead the new marketing initiative.</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>彼女が新しいマーケティング施策の先頭に立ちます。</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="50" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0177</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>galvanize</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>奮い立たせる</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>The CEO's speech galvanized the entire team.</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>CEOのスピーチはチーム全体を奮い立たせました。</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="50" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0178</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>entail</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>伴う・必要とする</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>This role entails frequent travel overseas.</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>この役職は頻繁な海外出張を伴います。</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="50" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0179</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>underscore</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>強調する</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>The report underscores the need for faster decision-making.</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>その報告書は迅速な意思決定の必要性を強調しています。</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="50" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0180</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>corroborate</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>裏付ける</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>The new data corroborates our initial findings.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>新しいデータは当初の調査結果を裏付けています。</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="50" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0181</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>substantiate</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>立証する</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>We need more evidence to substantiate this claim.</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>この主張を立証するにはもっと証拠が必要です。</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="50" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0182</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>reconcile</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>一致させる・調整する</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>We need to reconcile the two accounts by Friday.</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>金曜日までに2つの帳簿を一致させる必要があります。</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>会計で「（帳簿を）照合する」という意味でよく使われる。</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="50" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0183</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>impede</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>妨げる</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Poor communication impeded the project's progress.</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>コミュニケーション不足がプロジェクトの進行を妨げました。</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="50" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0184</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>curtail</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>削減する・切り詰める</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>The company had to curtail spending due to falling profits.</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>利益減少のため、その会社は支出を削減せざるを得ませんでした。</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="50" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0185</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>bolster</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>強化する・支える</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>The new hire will help bolster our engineering team.</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>新入社員は私たちのエンジニアリングチームを強化する助けになるでしょう。</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="50" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0186</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>hedge</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>リスクヘッジする</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>The company hedged against currency risk.</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>その会社は為替リスクをヘッジしました。</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="50" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0187</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>arbitrary</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>恣意的な</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>The decision seemed arbitrary and lacked clear reasoning.</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>その決定は恣意的で、明確な根拠に欠けているように見えました。</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="50" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0188</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>discretionary</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>裁量による</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Managers have discretionary authority over small purchases.</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>マネージャーは少額の購入について裁量権を持っています。</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="50" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0189</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>onerous</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>煩わしい・負担の大きい</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>The new compliance requirements are quite onerous.</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>新しいコンプライアンス要件はかなり負担が大きいです。</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="50" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0190</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>punitive</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>懲罰的な</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>The court imposed punitive damages on the company.</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>裁判所はその会社に懲罰的損害賠償を科しました。</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="50" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0191</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>protracted</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>長引く</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>The negotiations turned into a protracted dispute.</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>交渉は長引く紛争になりました。</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="50" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0192</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>unequivocal</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>明確な・紛れもない</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>The board gave its unequivocal support to the plan.</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>取締役会はその計画に対し明確な支持を示しました。</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="50" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0193</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>微妙な違いのある</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>The issue requires a more nuanced approach.</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>この問題にはより繊細なアプローチが必要です。</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="50" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0194</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>pragmatic</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>実用的な・現実的な</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>We need a pragmatic solution, not an ideal one.</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>理想的な解決策ではなく、現実的な解決策が必要です。</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="50" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0195</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>incremental</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>漸進的な・段階的な</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>We're taking an incremental approach to the rollout.</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>展開には段階的なアプローチを取っています。</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="50" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0196</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>de facto</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>事実上の</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>English has become the de facto language of the meeting.</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>英語がその会議の事実上の共通言語になりました。</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="50" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0197</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>status quo</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>現状</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Some team members prefer to maintain the status quo.</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>一部のチームメンバーは現状維持を好みます。</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="50" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0198</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>modus operandi</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>仕事のやり方・常套手段</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Cutting costs first is his usual modus operandi.</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>まずコストを削減するのが彼のいつものやり方です。</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="50" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0199</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>quid pro quo</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>見返り・交換条件</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>The deal was seen as a quid pro quo arrangement.</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>その取引は交換条件的な取り決めと見なされました。</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="50" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>VOC-0200</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>par for the course</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>フレーズ</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>よくあること・想定内</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Delays like this are par for the course in construction.</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>建設業ではこのような遅れはよくあることです。</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vocabulary_list.xlsx
+++ b/vocabulary_list.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O451"/>
+  <dimension ref="A1:O551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28026,6 +28026,6456 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>VOC-0451</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>accrue</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>（利息・利益などが）発生する、積み重なる</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Interest will accrue on the unpaid balance from the due date.</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>未払い残高には支払期日から利息が発生します。</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>主に利息・休暇日数など、時間の経過とともに自然に増えていくものに使う。</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>VOC-0452</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>adhere to</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>（規則・方針などを）順守する</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>All contractors must adhere to the company's safety guidelines.</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>すべての請負業者は会社の安全ガイドラインを順守しなければなりません。</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>comply withとほぼ同義だが、adhere toはより「固く守る」ニュアンスが強い。</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>VOC-0453</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>advocate</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>（政策・意見などを）主張する、支持する</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>She advocates for a more flexible remote-work policy.</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>彼女はより柔軟なリモートワーク方針を主張しています。</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>「advocate for + 物事」の形をとる。名詞としても使われ、その場合は「支持者、擁護者」を意味する。</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>VOC-0454</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>align</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>（方針・目標などを）一致させる</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>We need to align our marketing strategy with the new brand vision.</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>新しいブランドビジョンにマーケティング戦略を合わせる必要があります。</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>「align A with B」の形が頻出。名詞形alignmentも合わせて覚えたい。</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>VOC-0455</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>amenity</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>設備、アメニティ</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>The office building offers amenities such as a gym and a rooftop terrace.</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>そのオフィスビルにはジムや屋上テラスなどの設備があります。</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>主に複数形amenitiesで使われ、施設・住居の付帯設備を指す。</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>VOC-0456</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>annualize</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>年換算する</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>The first-quarter results were annualized to estimate full-year revenue.</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>第1四半期の実績は年間収益を見積もるために年換算されました。</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>四半期や月次の数値を1年分に換算する際に使う財務用語。</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>VOC-0457</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>ascertain</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>（事実などを）確かめる、突き止める</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>We need to ascertain the cause of the delay before proceeding.</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>先に進む前に遅延の原因を確かめる必要があります。</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>find outよりフォーマルな語で、報告書やビジネス文書でよく使われる。</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>VOC-0458</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>assertive</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>自己主張の強い、断固とした</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Being assertive in negotiations doesn't mean being aggressive.</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>交渉で自己主張が強いことは攻撃的であることを意味しません。</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>aggressive（攻撃的）とは異なり、ポジティブな意味合いで使われることが多い。</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>VOC-0459</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>augment</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>増強する、補強する</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>The company plans to augment its sales team with five new hires.</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>会社は5名の新規採用で営業チームを増強する予定です。</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>increaseよりフォーマルで、既存のものに何かを追加して強化するニュアンス。</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>VOC-0460</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>autonomous</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>自律的な、独立した</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Each regional office operates as an autonomous business unit.</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>各地域オフィスは自律的な事業部門として運営されています。</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>「独立して意思決定できる」というニュアンス。自動運転車（autonomous vehicle）でも使われる。</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>VOC-0461</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>backlash</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>反発、反動</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>The price increase caused a backlash from loyal customers.</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>値上げは常連客からの反発を招きました。</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>「against」を伴い「backlash against ~」の形もよく使われる。</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>VOC-0462</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>barter</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>物々交換する</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>The two companies agreed to barter services instead of paying in cash.</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>両社は現金で支払う代わりにサービスを物々交換することに合意しました。</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>現金を介さない取引を指す。名詞としても同じ形で使われる。</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>VOC-0463</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>bespoke</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>注文仕立ての、オーダーメイドの</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>The consultancy offers bespoke solutions tailored to each client.</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>そのコンサルティング会社は各クライアントに合わせた特注のソリューションを提供します。</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>customizedよりイギリス英語的で、高級感・専門性のニュアンスを持つ。</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>VOC-0464</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>boilerplate</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>定型文、決まり文句</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>The contract's boilerplate clauses were reviewed quickly by the legal team.</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>契約書の定型条項は法務チームによって手早く確認されました。</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>契約書などで繰り返し使われる標準的な文言を指す。形容詞的にも使う。</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>VOC-0465</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>bona fide</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>正真正銘の、誠実な</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>This is a bona fide offer, not a negotiating tactic.</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>これは交渉術ではなく、正真正銘のオファーです。</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>ラテン語由来。genuineとほぼ同義でよりフォーマルな響き。</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>VOC-0466</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>bookkeeping</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>記帳、簿記</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Accurate bookkeeping is essential for tax reporting.</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>正確な記帳は税務申告に不可欠です。</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>accounting（会計）より実務的で日々の記録作業を指すことが多い。</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>VOC-0467</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>bottom-up</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>ボトムアップの、現場主導の</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>The new initiative takes a bottom-up approach, starting with employee feedback.</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>この新しい取り組みは従業員からのフィードバックから始まるボトムアップ方式です。</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>対義語はtop-down（トップダウン）。組織論・意思決定の文脈で頻出。</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>VOC-0468</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>boycott</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>不買運動をする、ボイコットする</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Consumers threatened to boycott the brand over its labor practices.</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>消費者はその労働慣行を理由にブランドの不買運動をすると警告しました。</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>名詞としても同形で使われる。</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>VOC-0469</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>breach</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>（契約・規則などに）違反する</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>The supplier breached the contract by missing three consecutive deadlines.</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>そのサプライヤーは3回連続で納期を守れず契約に違反しました。</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>名詞としても頻出（a breach of contract=契約違反）。</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>VOC-0470</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>仲介する、取り持つ</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>The consultant helped broker a deal between the two firms.</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>そのコンサルタントは両社間の取引の仲介を手伝いました。</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>名詞では「仲介業者（stockbroker等）」の意味でも頻出。</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>VOC-0471</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>bureaucracy</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>官僚制、お役所仕事</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Cutting through bureaucracy was the biggest challenge in launching the project.</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>官僚的な手続きを乗り越えることがプロジェクト立ち上げにおける最大の課題でした。</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>否定的なニュアンスで「無駄に複雑な手続き」を指すことが多い。</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>VOC-0472</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>buyout</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>（企業の）買収</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>The management team is considering a buyout of the struggling division.</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>経営陣は不振部門の買収を検討しています。</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>特に経営陣や従業員による自社買収（management buyout）の文脈でよく使われる。</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>VOC-0473</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>capital expenditure</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>設備投資、資本的支出</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Capital expenditure on new machinery rose by 15% this year.</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>新しい機械への設備投資は今年15％増加しました。</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>略称CapEx。運営費（operating expense）と対比される財務用語。</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>VOC-0474</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>但し書き、注意事項</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>I'll approve the proposal, with one caveat: we need a backup plan.</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>一つ但し書きをつけてこの提案を承認します。バックアップ計画が必要です。</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>「with a caveat」の形でよく使われる、条件付きの合意を示す語。</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>VOC-0475</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>centralize</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>一元化する、集中させる</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>The company decided to centralize its purchasing department.</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>会社は購買部門を一元化することに決めました。</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>対義語はdecentralize（分散化する）。</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>VOC-0476</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>clientele</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>顧客層</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>The boutique hotel has built a loyal clientele over the years.</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>そのブティックホテルは長年かけて忠実な顧客層を築いてきました。</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>customer baseとほぼ同義だが、フォーマルで特定の層を指すニュアンスがある。</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>VOC-0477</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>collaborate</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>協力する、共同作業する</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>The two departments will collaborate on the product launch.</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>2つの部署が製品発売に向けて協力します。</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>「collaborate with ~ on ...」の形で頻出。</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>VOC-0478</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>commensurate</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>釣り合った、相応の</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Salary will be commensurate with experience.</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>給与は経験に応じて決定されます。</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>求人広告で頻出の表現。「commensurate with ~」の形をとる。</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>VOC-0479</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>competence</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>能力、力量</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>The training program aims to build competence in project management.</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>この研修プログラムはプロジェクト管理における能力向上を目指しています。</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>形容詞形competentも合わせて覚えたい。</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>VOC-0480</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>（データなどを）まとめる、編集する</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>The team compiled the survey results into a single report.</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>チームはアンケート結果を1つの報告書にまとめました。</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>データや情報を集めて整理するというニュアンス。</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>VOC-0481</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>concede</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>（不本意ながら）認める</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>The manager conceded that the timeline was too aggressive.</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>マネージャーはスケジュールが厳しすぎたことを認めました。</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>admitより「不本意ながら」というニュアンスが強い。</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>VOC-0482</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>conglomerate</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>複合企業、コングロマリット</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>The conglomerate owns businesses in media, energy, and retail.</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>そのコングロマリットはメディア、エネルギー、小売の各事業を保有しています。</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>複数の異業種事業を傘下に持つ大企業グループを指す。</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>VOC-0483</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>constituent</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>構成要素、（選挙区の）有権者</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Employee satisfaction is a key constituent of overall productivity.</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>従業員満足度は全体的な生産性の重要な構成要素です。</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>「component」に近い意味と、政治文脈での「有権者」の意味の両方を持つ。</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>VOC-0484</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>consultancy</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>コンサルティング会社、コンサルティング業務</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>She left the firm to start her own consultancy.</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>彼女は自分のコンサルティング会社を立ち上げるために会社を辞めました。</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>consulting firmとほぼ同義。イギリス英語でより一般的。</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>VOC-0485</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>conversion rate</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>コンバージョン率、成約率</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>The new landing page improved our conversion rate by 8%.</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>新しいランディングページによりコンバージョン率が8％改善しました。</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>マーケティング分野で頻出。訪問者が購入・登録に至る割合を指す。</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>VOC-0486</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>cordial</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>友好的な、丁重な</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>The meeting ended on a cordial note despite the disagreement.</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>意見の相違があったものの、会議は友好的な雰囲気で終わりました。</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>friendlyよりフォーマルで、礼儀正しさを含んだ友好さを表す。</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>VOC-0487</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>correlate</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>相関する</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Higher employee engagement tends to correlate with lower turnover.</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>従業員エンゲージメントが高いほど離職率が低い傾向と相関します。</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>「correlate with ~」の形。因果関係ではなく相関関係を示す点に注意。</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>VOC-0488</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>counterpart</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>対応する相手、対応者</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>She'll be meeting with her counterpart from the Tokyo office.</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>彼女は東京オフィスの担当者と会う予定です。</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>同じ立場・役職の相手を指す語。</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>VOC-0489</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>courier</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>配送業者、宅配便</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Please send the documents by courier for same-day delivery.</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>当日配送のため、書類は宅配便で送ってください。</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>動詞としても「（人が）運ぶ」の意味で使われることがある。</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>VOC-0490</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>credentials</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>資格、経歴</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>The candidate's credentials made her the top choice for the role.</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>その候補者の経歴により、彼女はその職の最有力候補となりました。</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>通常複数形で使われ、学歴・資格・実績をまとめて指す。</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>VOC-0491</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>cumulative</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>累積的な</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>The cumulative effect of small delays added up to a missed deadline.</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>小さな遅延が積み重なった結果、納期を逃してしまいました。</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>「積み重なっていく」というニュアンスの語。</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>VOC-0492</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>decentralize</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>分散化する</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>The firm decided to decentralize decision-making to regional managers.</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>その会社は意思決定を地域マネージャーに分散させることを決めました。</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>対義語centralizeとセットで覚えたい。</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>VOC-0493</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>deficit</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>赤字、不足</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>The department is operating with a budget deficit this quarter.</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>その部署は今四半期、予算赤字の状態で運営されています。</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>surplus（黒字）の対義語。</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>VOC-0494</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>deploy</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>配置する、展開する</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>The IT team will deploy the new system across all branches next month.</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ITチームは来月、全支店に新システムを展開します。</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>人員配置とITシステム導入の両方の文脈で使われる。</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>VOC-0495</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>deputy</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>代理、副〜</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>The deputy manager will chair the meeting in her absence.</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>彼女の不在時は副マネージャーが会議の議長を務めます。</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>「deputy + 役職名」の形で「副〜」を表す（例：deputy CEO）。</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>VOC-0496</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>deregulate</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>規制緩和する</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>The industry was deregulated in the early 2000s.</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>その業界は2000年代初頭に規制緩和されました。</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>政府による規制を撤廃・緩和すること。名詞形deregulationも重要。</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>VOC-0497</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>designate</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>指定する、任命する</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>The board will designate a successor before the CEO retires.</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>取締役会はCEOの退任前に後継者を指定します。</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>「designate A as B」の形で「AをBに任命する」の意味になる。</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>VOC-0498</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>diligent</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>勤勉な、丹念な</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>The auditors were diligent in checking every transaction.</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>監査人はすべての取引を丹念にチェックしました。</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>名詞形diligence（due diligence=デューデリジェンス）も重要語。</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>VOC-0499</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>disclose</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>開示する、公表する</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Publicly traded companies must disclose their financial results quarterly.</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>上場企業は四半期ごとに財務結果を開示しなければなりません。</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>名詞形disclosure（情報開示）も頻出。</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>VOC-0500</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>dissolve</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>解散する、解消する</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>The joint venture was dissolved after five years.</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>その合弁事業は5年後に解消されました。</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>組織や契約関係を法的に終了させる際に使う語。</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>VOC-0501</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>accommodate</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>（要望・人数などに）応じる、収容する</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>The conference room can accommodate up to fifty guests.</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>その会議室は最大50名を収容できます。</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>要望に応える意味と、物理的に収容する意味の両方がある頻出語。</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>VOC-0502</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>accompany</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>同行する、伴う</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>A detailed manual will accompany each shipment.</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>各出荷には詳細なマニュアルが添付されます。</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>人だけでなく「書類が同封される」といった無生物主語でもよく使われる。</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>VOC-0503</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>accordingly</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>副詞</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>それに応じて</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Sales targets were revised, and the budget was adjusted accordingly.</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>販売目標が改訂され、それに応じて予算も調整されました。</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>前文を受けて「その結果として」の意味で文頭・文中に置かれる。</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>VOC-0504</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>accumulate</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>蓄積する、たまる</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Unused vacation days will accumulate up to a maximum of ten.</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>未使用の休暇日数は最大10日まで蓄積されます。</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Part5でよく問われる動詞。名詞形accumulationも押さえておきたい。</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>VOC-0505</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>acknowledge</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>（受領などを）認める、承認する</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Please acknowledge receipt of this email by replying within 24 hours.</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>このメールの受領確認として24時間以内に返信してください。</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>ビジネスメールで「受け取りました」と伝える定番表現。</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>VOC-0506</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>adjacent</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>隣接した</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>The new office is adjacent to the main train station.</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>新しいオフィスは主要駅に隣接しています。</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>「adjacent to ~」の形で頻出。TOEIC Part7の地図問題でもよく登場する。</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>VOC-0507</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>adjust</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>調整する</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Please adjust the schedule to accommodate the client's request.</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>クライアントの要望に応じてスケジュールを調整してください。</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>名詞形adjustmentもPart5・7で頻出。</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>VOC-0508</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>advantageous</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>有利な</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Signing the contract now would be advantageous for both parties.</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>今契約に署名することは双方にとって有利でしょう。</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>beneficialとほぼ同義。Part5の語彙問題で頻出。</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>VOC-0509</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>affordable</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>手頃な価格の</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>The company offers affordable pricing plans for small businesses.</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>その会社は中小企業向けに手頃な価格プランを提供しています。</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>affordの形容詞形。cheapよりポジティブな響きを持つ。</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>VOC-0510</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>alternative</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>代わりの、代替の</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>We should consider an alternative supplier in case of delays.</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>遅延に備えて代替のサプライヤーを検討すべきです。</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>名詞としても頻出（an alternative to ~ =~の代替案）。</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>VOC-0511</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>anticipated</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>予想された、見込まれる</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>The anticipated revenue growth did not materialize this quarter.</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>予想されていた収益成長は今四半期実現しませんでした。</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>動詞anticipateの過去分詞が形容詞化した形。Part5で頻出。</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>VOC-0512</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>applicable</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>適用可能な、該当する</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>This discount is applicable only to first-time customers.</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>この割引は初回のお客様のみに適用されます。</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>「applicable to ~」の形。契約書・案内文で頻出。</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>VOC-0513</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>appreciable</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>かなりの、目に見えるほどの</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>There has been an appreciable increase in customer complaints.</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>顧客からの苦情がかなり増加しています。</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>noticeableに近い意味。appreciate（感謝する）と混同しないよう注意。</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>VOC-0514</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>appropriate</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>適切な</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Please wear appropriate attire for the client meeting.</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>クライアントとの会議には適切な服装で来てください。</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>動詞としても使われ、その場合は「充当する、流用する」の意味になる。</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>VOC-0515</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>approximately</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>副詞</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>おおよそ</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>The renovation will take approximately three months to complete.</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>改装工事の完了にはおおよそ3ヶ月かかります。</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>aboutよりフォーマルな語で、数字の前によく置かれる。</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>VOC-0516</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>assurance</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>保証、確約</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>The vendor gave assurance that the delivery would arrive on time.</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>ベンダーは配送が時間通りに到着することを保証しました。</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>動詞assureの名詞形。quality assurance（品質保証）でも頻出。</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>VOC-0517</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>attentive</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>注意深い、気配りのある</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>The staff were attentive to every guest's needs.</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>スタッフはすべてのゲストのニーズに気を配っていました。</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>カスタマーサービスの文脈で頻出の形容詞。</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>VOC-0518</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>authorization</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>名詞</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>許可、承認</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>You will need authorization from your manager to access this file.</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>このファイルにアクセスするには上司の許可が必要です。</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>動詞authorizeの名詞形。「prior authorization」の形もよく使われる。</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>VOC-0519</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>beneficial</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>有益な</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Attending the workshop will be beneficial for new employees.</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>そのワークショップへの参加は新入社員にとって有益でしょう。</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>「beneficial to/for ~」の形で頻出。</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>VOC-0520</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>capable</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>能力がある</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>She is fully capable of managing the project on her own.</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>彼女は単独でそのプロジェクトを管理する能力を十分に備えています。</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>「capable of ~ing」の形をとる点に注意（capable to ~とは言わない）。</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>VOC-0521</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>comparable</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>匹敵する、同程度の</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Our prices are comparable to those of our competitors.</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>当社の価格は競合他社と同程度です。</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>「comparable to ~」の形。similar toと似ているが「比較して同水準」というニュアンス。</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>VOC-0522</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>complimentary</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>無料の、サービスの</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>All guests receive a complimentary breakfast.</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>すべてのゲストに無料の朝食が提供されます。</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>complementary（補完的な）とスペルが似ているが意味が異なるので注意。TOEIC頻出の引っかけ語。</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>VOC-0523</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>comprehend</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>理解する</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Some employees struggled to comprehend the new policy.</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>一部の従業員は新しい方針を理解するのに苦労しました。</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>understandよりフォーマルな語。</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>VOC-0524</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>conclude</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>結論づける、終える</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>The committee concluded that further research was needed.</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>委員会はさらなる調査が必要であると結論づけました。</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>「会議を終える」の意味でも使われる（conclude the meeting）。</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>VOC-0525</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>conducive</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>（〜に）役立つ、resulting in</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>A quiet workspace is conducive to better concentration.</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>静かな職場はより高い集中力に役立ちます。</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>「conducive to ~」の形で頻出のPart5語彙。</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>VOC-0526</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>consecutive</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>連続した</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>The team hit its sales target for six consecutive months.</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>チームは6ヶ月連続で販売目標を達成しました。</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>「連続する回数」を表す際に数字の前に置く。</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>VOC-0527</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>considerable</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>かなりの、相当な</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>The merger required considerable investment in new systems.</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>その合併には新システムへのかなりの投資が必要でした。</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>considerate（思いやりのある）と混同しやすいので注意。</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>VOC-0528</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>consult</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>相談する、参照する</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Please consult the manual before contacting technical support.</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>テクニカルサポートに連絡する前にマニュアルを参照してください。</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>「consult with 人」「consult 資料」の両方の形をとる。</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>VOC-0529</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>contribute</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>貢献する、寄与する</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Every team member contributed to the project's success.</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>チームの全員がプロジェクトの成功に貢献しました。</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>「contribute to ~」の形。名詞形contributionも重要。</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>VOC-0530</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>designated</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>指定された</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Smoking is only permitted in designated areas.</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>喫煙は指定された場所でのみ許可されています。</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>動詞designateの過去分詞が形容詞化した形。標識や案内文で頻出。</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>VOC-0531</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>despite</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>前置詞</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>〜にもかかわらず</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Despite the tight deadline, the team delivered high-quality work.</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>厳しい締め切りにもかかわらず、チームは質の高い成果を出しました。</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>後ろに名詞・動名詞をとる前置詞。althoughと混同しやすいので注意（Part5頻出）。</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>VOC-0532</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>determine</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>決定する、判断する</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Further tests will determine the root cause of the defect.</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>さらなる検査が不具合の根本原因を判断します。</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>decideより「調査・分析の結果として判断する」ニュアンスが強い。</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>VOC-0533</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>distribute</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>配布する、流通させる</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>The handouts will be distributed at the start of the seminar.</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>資料はセミナーの開始時に配布されます。</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>名詞形distributionも重要。</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>VOC-0534</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>durable</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>耐久性のある</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>The packaging is designed to be durable during long-distance shipping.</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>この梱包は長距離輸送でも耐久性があるよう設計されています。</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>durable goods（耐久財）という経済用語でも使われる。</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>VOC-0535</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>emphasize</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>強調する</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>The manager emphasized the importance of meeting the deadline.</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>マネージャーは締め切りを守ることの重要性を強調しました。</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>stressとほぼ同義。名詞形emphasisも覚えておきたい。</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>VOC-0536</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>enclosed</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>同封された</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Please find the enclosed invoice for your records.</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>記録用として同封の請求書をご確認ください。</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>メールや手紙で「Please find enclosed ~」の形で頻出。</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>VOC-0537</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>ensure</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>確実にする、保証する</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Please ensure that all fields are filled out correctly.</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>すべての項目が正しく記入されていることを確認してください。</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>「ensure that節」の形が頻出。TOEIC最頻出動詞の一つ。</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>VOC-0538</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>entitled</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>（〜する）権利がある</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Full-time employees are entitled to two weeks of paid leave.</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>正社員は2週間の有給休暇を取得する権利があります。</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>「be entitled to ~」の形。福利厚生の説明で頻出。</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>VOC-0539</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>exceed</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>超える</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>This month's sales exceeded expectations by a wide margin.</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>今月の売上は予想を大きく上回りました。</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>exceptと混同しやすい頻出の引っかけ語。</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>VOC-0540</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>exceptional</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>並外れた、例外的な</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>The client praised the team for its exceptional customer service.</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>クライアントはそのチームの並外れた顧客サービスを称賛しました。</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>excellentより強い賞賛のニュアンスを持つ。</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>VOC-0541</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>exclusively</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>副詞</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>もっぱら、独占的に</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>This offer is available exclusively to premium members.</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>このオファーはプレミアム会員限定でご利用いただけます。</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>形容詞exclusive（独占的な、高級な）とセットで覚えたい。</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>VOC-0542</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>extend</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>延長する、拡大する</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>The company decided to extend the warranty period by six months.</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>会社は保証期間を6ヶ月延長することを決めました。</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>「感謝を伝える」の意味でも使われる（extend our gratitude）。</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>VOC-0543</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>favorable</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>好意的な、有利な</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>The client reviews have been overwhelmingly favorable.</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>クライアントのレビューは圧倒的に好意的でした。</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>「favorable terms（有利な条件）」のように契約文脈でも頻出。</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>VOC-0544</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>forthwith</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>副詞</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>直ちに、即座に</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>All outstanding invoices must be settled forthwith.</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>未払いの請求書はすべて直ちに決済されなければなりません。</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>immediatelyの非常にフォーマルな同義語。契約書・通知文で見られる。</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>VOC-0545</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>壊れやすい</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Please label the package as fragile before shipping.</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>発送前に荷物に「壊れ物」のラベルを貼ってください。</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>荷物の梱包・配送の文脈で頻出。</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>VOC-0546</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>gradually</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>副詞</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>徐々に</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>The new system will be gradually rolled out across all locations.</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>新システムは全拠点に徐々に展開されます。</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>suddenlyの対義語的な位置づけの副詞。</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>VOC-0547</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>notify</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>動詞</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>通知する</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Please notify us immediately of any changes to your contact information.</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>連絡先情報に変更があった場合は直ちにお知らせください。</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>「notify 人 of 事柄」の形。名詞形notificationも重要。</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>VOC-0548</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>renowned</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>著名な、名高い</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>The firm hired a renowned architect to design the new headquarters.</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>その会社は新本社の設計に著名な建築家を起用しました。</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>「renowned for ~」の形で「〜で有名な」の意味にもなる。</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>VOC-0549</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>resourceful</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>臨機応変な、機知に富んだ</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>The team was resourceful in finding a solution despite the budget cuts.</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>チームは予算削減にもかかわらず、臨機応変に解決策を見つけました。</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>限られた資源の中で工夫できる能力を褒める語。</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>VOC-0550</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>単語</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>形容詞</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>有効な</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>This coupon is valid until the end of the month.</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>このクーポンは月末まで有効です。</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>invalid（無効な）と対で覚えておきたい。契約・チケット等の有効期限で頻出。</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
